--- a/areas/lac/inputs/scenarios/root_workbooks/A-O_Demand.xlsx
+++ b/areas/lac/inputs/scenarios/root_workbooks/A-O_Demand.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -725,6 +725,11 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Measured_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -849,6 +854,11 @@
       <c r="AJ2" t="n">
         <v>1636.45</v>
       </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -973,6 +983,11 @@
       <c r="AJ3" t="n">
         <v>108.78</v>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1097,6 +1112,11 @@
       <c r="AJ4" t="n">
         <v>6362.75</v>
       </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1221,6 +1241,11 @@
       <c r="AJ5" t="n">
         <v>7.74</v>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1345,6 +1370,11 @@
       <c r="AJ6" t="n">
         <v>1297.45</v>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,6 +1499,11 @@
       <c r="AJ7" t="n">
         <v>648.78</v>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1593,6 +1628,11 @@
       <c r="AJ8" t="n">
         <v>79.29000000000001</v>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1717,6 +1757,11 @@
       <c r="AJ9" t="n">
         <v>331.06</v>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1841,6 +1886,11 @@
       <c r="AJ10" t="n">
         <v>458.78</v>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1965,6 +2015,11 @@
       <c r="AJ11" t="n">
         <v>156.43</v>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2089,6 +2144,11 @@
       <c r="AJ12" t="n">
         <v>111.19</v>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2213,6 +2273,11 @@
       <c r="AJ13" t="n">
         <v>2779.28</v>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2337,6 +2402,11 @@
       <c r="AJ14" t="n">
         <v>67.58</v>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2461,6 +2531,11 @@
       <c r="AJ15" t="n">
         <v>141.54</v>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2585,6 +2660,11 @@
       <c r="AJ16" t="n">
         <v>786.72</v>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2709,6 +2789,11 @@
       <c r="AJ17" t="n">
         <v>258.69</v>
       </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2833,6 +2918,11 @@
       <c r="AJ18" t="n">
         <v>102.67</v>
       </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2957,6 +3047,11 @@
       <c r="AJ19" t="n">
         <v>89.84999999999999</v>
       </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3080,6 +3175,11 @@
       </c>
       <c r="AJ20" t="n">
         <v>19.59</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>bus-bar</t>
+        </is>
       </c>
     </row>
   </sheetData>
